--- a/data/trans_camb/P43E-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43E-Edad-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>10,62</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>10,62</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 2,99</t>
+          <t>-15,13; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 34,91</t>
+          <t>-7,08; 32,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 2,99</t>
+          <t>-15,13; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 34,91</t>
+          <t>-7,08; 32,05</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 20,04</t>
+          <t>-58,12; 15,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 200,68</t>
+          <t>-31,28; 168,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 20,04</t>
+          <t>-58,12; 15,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 200,68</t>
+          <t>-31,28; 168,16</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -0,59</t>
+          <t>-12,29; -0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 2,77</t>
+          <t>-8,55; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -0,59</t>
+          <t>-12,29; -0,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 2,77</t>
+          <t>-8,55; 8,32</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-30,08%</t>
+          <t>-0,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-30,08%</t>
+          <t>-0,46%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -2,44</t>
+          <t>-40,95; -1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 11,09</t>
+          <t>-28,73; 34,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -2,44</t>
+          <t>-40,95; -1,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 11,09</t>
+          <t>-28,73; 34,18</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -1,39</t>
+          <t>-11,91; -1,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,42</t>
+          <t>-5,12; 7,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -1,39</t>
+          <t>-11,91; -1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,42</t>
+          <t>-5,12; 7,07</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -5,06</t>
+          <t>-40,91; -7,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 31,32</t>
+          <t>-17,6; 29,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -5,06</t>
+          <t>-40,91; -7,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 31,32</t>
+          <t>-17,6; 29,31</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>6,66</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -3,77</t>
+          <t>-14,52; -3,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 9,58</t>
+          <t>0,49; 12,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -3,77</t>
+          <t>-14,52; -3,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 9,58</t>
+          <t>0,49; 12,03</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,25; -16,29</t>
+          <t>-52,92; -17,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 43,3</t>
+          <t>1,75; 57,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,25; -16,29</t>
+          <t>-52,92; -17,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 43,3</t>
+          <t>1,75; 57,13</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,42</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 1,88</t>
+          <t>-11,22; 1,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,27</t>
+          <t>-3,15; 10,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 1,88</t>
+          <t>-11,22; 1,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,27</t>
+          <t>-3,15; 10,14</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 11,4</t>
+          <t>-49,68; 12,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 62,32</t>
+          <t>-13,6; 74,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 11,4</t>
+          <t>-49,68; 12,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 62,32</t>
+          <t>-13,6; 74,17</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,91</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 7,59</t>
+          <t>-8,26; 7,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 10,88</t>
+          <t>-2,75; 10,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 7,59</t>
+          <t>-8,26; 7,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 10,88</t>
+          <t>-2,75; 10,5</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 89,86</t>
+          <t>-50,66; 78,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 131,2</t>
+          <t>-16,54; 122,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 89,86</t>
+          <t>-50,66; 78,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 131,2</t>
+          <t>-16,54; 122,64</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 3,8</t>
+          <t>-16,03; 3,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 7,52</t>
+          <t>-8,42; 7,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 3,8</t>
+          <t>-16,03; 3,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 7,52</t>
+          <t>-8,42; 7,92</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-2,81%</t>
+          <t>-1,14%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-2,81%</t>
+          <t>-1,14%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 50,31</t>
+          <t>-78,43; 62,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 98,04</t>
+          <t>-42,76; 117,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 50,31</t>
+          <t>-78,43; 62,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 98,04</t>
+          <t>-42,76; 117,83</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
     </row>
